--- a/docs/02_基本設計/03_データ設計/KF-BD-005_コード定義書.xlsx
+++ b/docs/02_基本設計/03_データ設計/KF-BD-005_コード定義書.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改訂履歴" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="コード一覧" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申請状態遷移" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="業務ルール定数" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -70,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -125,11 +131,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -150,6 +162,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -574,7 +593,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -605,6 +624,8 @@
       </c>
       <c r="D12" s="9" t="n"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -651,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -733,6 +754,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装の定数クラス（RequestType / RequestStatus / LeaveUnit / StepStatus / NotificationType）と照合し、全コード値が一致していることを確認。画面表示ラベル・承認段の作成条件（上長なし／無効は 2 段目のみ）・通知の宛先・バッチ未実装（BAT-001/002）を備考に追記。申請状態遷移を実装に合わせて修正。業務ルール定数シートを追加</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>休憩・離席の機能追加に伴い、申請種別 BREAK_CORRECTION、休憩・離席種別（BREAK / AWAY）、承認ステップの表示専用状態 SKIPPED（DB 非保存）を追加。申請状態遷移に休憩・離席修正申請の検査・反映と SKIPPED の扱いを追記。業務ルール定数のパスワードポリシー（管理者設定にも適用）と休憩・離席の控除ルールを実装に合わせて更新し、休憩・離席の同時継続制約を追加</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -746,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -806,7 +873,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>一般の利用者</t>
+          <t>一般の利用者。画面表示は「社員」</t>
         </is>
       </c>
     </row>
@@ -833,7 +900,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>部下の申請を承認</t>
+          <t>部下の申請を承認（1段目）。直属の部下の月次集計を閲覧</t>
         </is>
       </c>
     </row>
@@ -860,7 +927,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>システム管理・最終承認</t>
+          <t>システム管理・最終承認（2段目）。画面表示は「管理者」</t>
         </is>
       </c>
     </row>
@@ -885,7 +952,11 @@
           <t>有効</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>画面表示は「在籍」</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -910,7 +981,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>退職・休職等。ログイン不可</t>
+          <t>退職・休職等。ログイン不可（E-001）。既発行トークンも次のリクエストで 401。物理削除はしない</t>
         </is>
       </c>
     </row>
@@ -963,25 +1034,29 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>取得単位</t>
+          <t>申請種別</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>requests.unit</t>
+          <t>requests.request_type</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>FULL</t>
+          <t>BREAK_CORRECTION</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>全日</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr"/>
+          <t>休憩・離席修正申請</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>対象日の休憩・離席の区間（種別・開始・終了）の追加・修正を申請する。承認は休暇・打刻修正と同じ 2 段階。最終承認で attendance_breaks に反映し、勤務・残業時間を再計算（V5）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -996,17 +1071,17 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>FULL</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>午前半休</t>
+          <t>全日</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>0.5日</t>
+          <t>1.0日。画面表示は「1日」</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1098,12 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>午後半休</t>
+          <t>午前半休</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1040,27 +1115,27 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>申請状態</t>
+          <t>取得単位</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>requests.status</t>
+          <t>requests.unit</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>DRAFT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>下書き</t>
+          <t>午後半休</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>未提出</t>
+          <t>0.5日</t>
         </is>
       </c>
     </row>
@@ -1077,17 +1152,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>DRAFT</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>承認待ち</t>
+          <t>下書き</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>承認フロー進行中</t>
+          <t>未提出。本人のみ閲覧・提出・取下げ可</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1179,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>RETURNED</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>差戻し</t>
+          <t>承認待ち</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>申請者が修正して再提出可能</t>
+          <t>承認フロー進行中（requests.current_step＝処理中の段）</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1206,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>RETURNED</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>差戻し</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>終了。再提出不可</t>
+          <t>申請者が提出（API-022）で再提出可能。取下げも可</t>
         </is>
       </c>
     </row>
@@ -1158,17 +1233,17 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>承認済み</t>
+          <t>却下</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>終了。休暇残日数・打刻へ反映済み</t>
+          <t>終了。再提出不可</t>
         </is>
       </c>
     </row>
@@ -1185,42 +1260,46 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>取下げ</t>
+          <t>承認済み</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>終了</t>
+          <t>終了。休暇残日数・打刻へ反映済み。承認済みの取消・取下げは不可（E-011）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>承認ステップ状態</t>
+          <t>申請状態</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>approval_steps.status</t>
+          <t>requests.status</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>WAITING</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>処理待ち</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+          <t>取下げ</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>終了。下書き・承認待ち・差戻しから取下げ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -1235,15 +1314,19 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>APPROVED</t>
+          <t>WAITING</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>承認</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr"/>
+          <t>処理待ち</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>画面表示は「承認待ち」</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1258,12 +1341,12 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>RETURNED</t>
+          <t>APPROVED</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>差戻し</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
@@ -1281,12 +1364,12 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>RETURNED</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>差戻し</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
@@ -1294,216 +1377,212 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>日数ルール</t>
+          <t>承認ステップ状態</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>leave_types.max_days_rule</t>
+          <t>approval_steps.status</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>LIMITED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>上限付き</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>残日数の範囲内でのみ取得可</t>
-        </is>
-      </c>
+          <t>却下</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>日数ルール</t>
+          <t>承認ステップ状態</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>leave_types.max_days_rule</t>
+          <t>approval_steps.status</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>UNLIMITED</t>
+          <t>SKIPPED</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>無制限</t>
+          <t>処理なし</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>日数による上限管理をしない</t>
+          <t>表示専用の値で DB には保存しない（DB の値は WAITING のまま）。承認履歴 API（API-007）が、取下げ・差戻し・却下で打ち切られ未処理で残った WAITING の段を返すときの値。画面は「処理なし」と表示</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>承認段</t>
+          <t>日数ルール</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>approval_steps.step_no</t>
+          <t>leave_types.max_days_rule</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>LIMITED</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>上長</t>
+          <t>上限付き</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>申請者の上長</t>
+          <t>残日数の範囲内でのみ取得可</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>承認段</t>
+          <t>日数ルール</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>approval_steps.step_no</t>
+          <t>leave_types.max_days_rule</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>UNLIMITED</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>無制限</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>人事（ADMIN）</t>
+          <t>日数による上限管理をしない</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>休憩・離席種別</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>notifications.type</t>
+          <t>attendance_breaks.kind／requests.corrected_break_kind</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>REQUEST_SUBMITTED</t>
+          <t>BREAK</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>申請提出（承認依頼）</t>
+          <t>休憩</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>承認者宛。提出・再提出時（ONL-005 / ONL-022）、1段目承認後の次段通知（ONL-010）</t>
+          <t>昼休みなど。打刻した日は打刻合計を休憩として控除（打刻がない日は法定休憩を自動控除）。画面表示は「休憩」</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>休憩・離席種別</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>notifications.type</t>
+          <t>attendance_breaks.kind／requests.corrected_break_kind</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>REQUEST_APPROVED</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>承認</t>
+          <t>離席</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>申請者宛。1段目承認・最終承認時（ONL-010）</t>
+          <t>日中離席（私用外出など）。打刻した時間は全て勤務時間から控除。画面表示は「離席」</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>承認段</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>notifications.type</t>
+          <t>approval_steps.step_no</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>REQUEST_RETURNED</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>差戻し</t>
+          <t>上長</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>申請者宛（ONL-011）</t>
+          <t>申請者の上長（users.manager_id）が有効（ACTIVE）なときのみ作成。上長なし・無効のときは 2 段目の 1 行だけ作る</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>通知種別</t>
+          <t>承認段</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>notifications.type</t>
+          <t>approval_steps.step_no</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>REQUEST_REJECTED</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>却下</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>申請者宛（ONL-012）</t>
+          <t>人事（ADMIN）。申請者以外の有効な全管理者が処理可（approver_id は処理した管理者で確定）</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1599,17 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>REQUEST_WITHDRAWN</t>
+          <t>REQUEST_SUBMITTED</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>取下げ</t>
+          <t>申請提出（承認依頼）</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>承認者宛。承認待ち（PENDING）の取下げ時のみ（ONL-008）</t>
+          <t>承認者宛。提出・再提出時（ONL-005 / ONL-022）は現在の段の承認者（1 段目は指名された上長、2 段目は申請者以外の有効な全管理者）、1 段目承認後は 2 段目の管理者全員へ（ONL-010）</t>
         </is>
       </c>
     </row>
@@ -1547,17 +1626,17 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>LEAVE_GRANTED</t>
+          <t>REQUEST_APPROVED</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>休暇付与</t>
+          <t>承認</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>本人宛。付与・調整時（ONL-017、BAT-001）。request_id は空</t>
+          <t>申請者宛。1 段目承認時（管理者の最終承認待ちである旨）・最終承認時（ONL-010）</t>
         </is>
       </c>
     </row>
@@ -1574,17 +1653,125 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
+          <t>REQUEST_RETURNED</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>差戻し</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>申請者宛（ONL-011）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>通知種別</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>notifications.type</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>REQUEST_REJECTED</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>却下</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>申請者宛（ONL-012）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>通知種別</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>notifications.type</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>REQUEST_WITHDRAWN</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>取下げ</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>現在の承認者宛。承認待ち（PENDING）の取下げ時のみ（ONL-008）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>通知種別</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>notifications.type</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>LEAVE_GRANTED</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>休暇付与</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>本人宛。管理者の付与・日数調整時（ONL-017）。自動付与（BAT-001）はアプリ内に実装なし（未実装）。request_id は空</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>通知種別</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>notifications.type</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
           <t>LEAVE_ALERT</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>休暇アラート</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>本人宛。年5日取得義務の未達アラート（BAT-002）。request_id は空</t>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>本人宛。年5日取得義務の未達アラート（BAT-002）。発行元のバッチが未実装のため現状は発行されない（画面は受信すれば表示する）。request_id は空</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1847,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>API-005（asDraft=true）</t>
+          <t>API-005（asDraft=true）。入力形式のみ検証（残日数・重複は提出時）</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1874,7 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>入力チェックOK・残日数／期間重複OK。新規は API-005、DRAFT / RETURNED は API-022。再提出時は承認ルートを作り直す</t>
+          <t>入力チェックOK・残日数／期間重複OK。新規は API-005、DRAFT / RETURNED は API-022。再提出時は承認ルートを作り直す。休憩・離席修正申請は提出時に、出勤打刻の有無・時刻の前後と範囲・既存区間との重複を検査（E-003 / E-005）し、同日・同種別の承認待ちがあれば E-005。上長が有効なら 1 段目、いなければ 2 段目から開始</t>
         </is>
       </c>
     </row>
@@ -1709,10 +1896,14 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>上長</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
+          <t>上長（指名された本人）</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>申請者と 2 段目の管理者へ通知</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1737,7 +1928,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>休暇残日数・打刻を更新</t>
+          <t>休暇：残日数を消化（失効日の早い付与行から。上限付き種別のみ）／打刻修正：attendance_records を登録・更新し、その日の休憩・離席を考慮して勤務・残業時間を再計算／休憩・離席修正：attendance_breaks の同種別の継続中の区間を修正（無ければ追加）、退勤済みなら勤務・残業時間を再計算（承認時にも提出時と同じ検査を行う）</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1955,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>コメント必須</t>
+          <t>コメント必須。申請者へ通知</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1982,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>コメント必須</t>
+          <t>コメント必須。申請者へ通知。終了（再提出不可）</t>
         </is>
       </c>
     </row>
@@ -1818,7 +2009,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>承認前のみ</t>
+          <t>承認前のみ。PENDING の取下げは現在の承認者へ通知。取下げ・差戻し・却下で打ち切られ未処理で残った承認ステップは、表示上 SKIPPED（処理なし）。APPROVED / REJECTED / WITHDRAWN は取下げ不可（E-011）、提出は E-016</t>
         </is>
       </c>
     </row>
@@ -1826,4 +2017,355 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>※実装の定数・業務ルール（コード値ではないが設計に影響するもの）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>値</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>備考（実装箇所・補足）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>ログイン失敗の上限回数</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>5 回</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>AuthService.MAX_FAILED_ATTEMPTS。到達でロックし失敗回数を 0 に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>アカウントロック時間</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>30 分</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>AuthService.LOCK_MINUTES（users.locked_until）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>パスワード最小長</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>12 文字</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>AuthService.MIN_PASSWORD_LENGTH。半角英字と半角数字を両方含む・現在と異なる・UTF-8 で 72 バイト以内。管理者による初期設定・再設定（UserService#checkPolicy → AuthService.validatePolicy）にも同じポリシーを適用する（12〜72 文字・半角英字と数字を両方含む。DTO は半角英数字記号のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>JWT 有効期間</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>2 時間</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>kintaiflow.jwt.expiration-hours。HS256</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>業務タイムゾーン</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Asia/Tokyo</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>AppTime.ZONE／Clock Bean。DB 接続も SET TIME ZONE 'Asia/Tokyo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>休暇申請の最大期間</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>1,100 日</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>RequestService.MAX_PERIOD_DAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>休暇日数の計算</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>土日・祝日（holidays）を除く営業日数。半休（AM/PM）は 0.5 日（営業日でなければ 0 日で E-002）</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>RequestService#calcDays</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>申請理由・付与調整理由の最大長</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>200 文字</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>requests.reason／付与の note</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>承認コメントの最大長</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>500 文字</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>ApprovalCommentRequest</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>通知メッセージの最大長・一覧件数</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>500 文字（超過は切り詰め）／最新 50 件</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>NotificationService</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>手動付与の日数範囲</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>0.1〜99.9 日（小数 1 位）</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>付与日は入社日以降・本日以前・2 年以内（E-014）。上限付き（LIMITED）かつ有効な種別のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>付与行の失効日</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>付与日の 2 年後</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>LeaveBalanceService#grant（leave_balances.expires_on）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>法定付与日数（勤続月数）</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>6 か月未満 0／6〜17 か月 10／18〜29 か月 11／30〜41 か月 12／42〜53 か月 14／54〜65 か月 16／66〜77 か月 18／78 か月以上 20</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>LeaveBalanceService#statutoryDays。次回付与予定日（nextGrantDate）は入社日＋6 か月を初回とし 1 年ごと（API-017 の nextStatutoryDays に使用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>年5日取得義務</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>付与 10 日以上の年休付与行（付与日から 1 年未満）が対象。期間は付与日〜翌年の前日、承認済み年休が 5 日未満なら未達</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>LeaveBalanceService#calcMandatory5（API-013 の mandatory5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>年次有給休暇の種別名</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>年次有給休暇</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>leave_types.name。名称・有給区分・日数ルール・有効フラグは変更不可（E-016）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>休憩・離席の控除・所定時間</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>離席（AWAY）は打刻した時間を全て控除。休憩（BREAK）は 1 回でも打刻した日は打刻合計を控除し、打刻がない日は法定休憩を自動控除（離席を除いた拘束 6 時間超 → 45 分、8 時間超 → 60 分）。所定 480 分を超えた分が残業</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>AttendanceCalculator#calculate（出勤・退勤・区間）。区間は出勤〜退勤に切り詰めて分単位（切り捨て）で計算し、終了していない区間は無視する。休憩不足（法定未満）の警告は未実装</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>休憩・離席の同時継続</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>1 勤務日に開始中の区間は 1 つ</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>attendance_breaks の部分ユニーク索引 uq_attendance_breaks_open（end_at IS NULL）。違反は E-020。開始中は退勤不可（E-022）。打刻した区間の取消・削除、0 分の区間の自動破棄は未実装</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>集計画面の 45 時間超表示</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>月間残業が 45 時間を超えると赤字・警告表示（画面のみ。通知・アラートは発行しない）</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>ManagerSummaryView（SCR-203）。36協定のアラートは未実装</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
 </file>